--- a/output/pdf_financials_xlsx/CYF.xlsx
+++ b/output/pdf_financials_xlsx/CYF.xlsx
@@ -2451,10 +2451,10 @@
         <v>0.000213</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.0009970000000000001</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.001549</v>
       </c>
     </row>
     <row r="35">
@@ -2567,10 +2567,10 @@
         <v>0.000213</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.0009970000000000001</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.001549</v>
       </c>
     </row>
     <row r="37">
@@ -3263,10 +3263,10 @@
         <v>0.038888</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.059138</v>
+        <v>0.058141</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.028484</v>
+        <v>0.026935</v>
       </c>
     </row>
     <row r="49">
@@ -7713,19 +7713,19 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.049014</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.231697</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.336876</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.332374</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.396755</v>
       </c>
       <c r="Q124" s="3" t="n">
         <v>0</v>
@@ -7771,19 +7771,19 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.049014</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.231697</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.336876</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.332374</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.396755</v>
       </c>
       <c r="Q125" s="3" t="n">
         <v>0</v>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -23819,7 +23819,11 @@
           <t>Principal portion of lease payments</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -38531,7 +38535,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -39119,7 +39123,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -39600,7 +39604,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -40374,7 +40378,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">

--- a/output/pdf_financials_xlsx/CYF.xlsx
+++ b/output/pdf_financials_xlsx/CYF.xlsx
@@ -2142,22 +2142,22 @@
         <v>0.108092</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.293252</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.477202</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.587024</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.478221</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.454107</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.357778</v>
       </c>
     </row>
     <row r="29">
@@ -2200,22 +2200,22 @@
         <v>-2.727332</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.850548</v>
+        <v>-3.557296</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.686066</v>
+        <v>-1.208864</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.179399</v>
+        <v>-2.592375</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-4.67649</v>
+        <v>-4.198269</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-4.478441</v>
+        <v>-4.024334</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-2.993999</v>
+        <v>-2.636221</v>
       </c>
     </row>
     <row r="30">
@@ -2258,22 +2258,22 @@
         <v>-36.46501663054257</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-38.26187049673434</v>
+        <v>-35.34790343362843</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-25.17267841146611</v>
+        <v>-18.04813377127501</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-35.45329867768767</v>
+        <v>-28.90742720859211</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-40.85287604338198</v>
+        <v>-36.6752335734222</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-34.28483652459178</v>
+        <v>-30.80840705735691</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-21.50343383522633</v>
+        <v>-18.93380854453665</v>
       </c>
     </row>
     <row r="31">
@@ -6287,25 +6287,25 @@
         <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.108092</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.293252</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.477202</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.587024</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.478221</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.454107</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.357778</v>
       </c>
     </row>
     <row r="101">
@@ -6980,7 +6980,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -6992,7 +6992,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.00775</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
@@ -7007,10 +7007,10 @@
         <v>0</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.104999</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>0.043137</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>0</v>
@@ -18881,7 +18881,11 @@
           <t>Depreciation on property and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -18978,7 +18982,11 @@
           <t>Depreciation on right-of-use assets (note 13)</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -19075,7 +19083,11 @@
           <t>Loss on disposal of property and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -21787,7 +21799,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -22276,7 +22292,11 @@
           <t>Depreciation on property and equipment</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -22369,7 +22389,11 @@
           <t>Depreciation on right-of-use assets</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -25773,7 +25797,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -30751,7 +30779,11 @@
           <t>Depreciation on property and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -30840,7 +30872,11 @@
           <t>Depreciation on right-of-use assets (note 13)</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -34290,7 +34326,11 @@
           <t>Depreciation on right-of-use assets (note 12)</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -35868,7 +35908,11 @@
           <t>Depreciation on right-of-use assets (note 11)</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CYF.xlsx
+++ b/output/pdf_financials_xlsx/CYF.xlsx
@@ -687,7 +687,7 @@
         <v>1.122001</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1.019285</v>
+        <v>0.476575</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>-0.134442</v>
@@ -919,7 +919,7 @@
         <v>1.323416</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.799619</v>
+        <v>2.979287</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>1.578891</v>
@@ -977,7 +977,7 @@
         <v>-0.201415</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.780334</v>
+        <v>-2.502712</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-1.713333</v>
@@ -1267,7 +1267,7 @@
         <v>-0.6484839999999999</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-1.126953</v>
+        <v>-1.640061</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-1.640061</v>
@@ -1567,7 +1567,7 @@
         <v>-0.6484839999999999</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-1.126953</v>
+        <v>-1.640061</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-1.640061</v>
@@ -1741,7 +1741,7 @@
         <v>-0.6484839999999999</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-1.126953</v>
+        <v>-1.640061</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-1.640061</v>
@@ -2057,7 +2057,7 @@
         <v>-0.6484839999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.126953</v>
+        <v>-1.640061</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.640061</v>
@@ -2173,7 +2173,7 @@
         <v>-0.6484839999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.9989479999999999</v>
+        <v>-1.512056</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.538581</v>
@@ -2231,7 +2231,7 @@
         <v>-15.66973142118426</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-28.90589959900019</v>
+        <v>-43.75336746664074</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-106.5168102162139</v>
@@ -2347,7 +2347,7 @@
         <v>-15.66973142118426</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-32.60989588125915</v>
+        <v>-47.4573637488997</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>-113.5423265203548</v>
@@ -3723,49 +3723,49 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>4.436759</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>4.436759</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>4.449078</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>4.488457</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>4.64982</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>4.72115</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>4.85128</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>4.882663</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>5.225182</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>5.897551</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>6.403675</v>
       </c>
       <c r="N56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>6.716721</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0</v>
+        <v>7.037994</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0</v>
+        <v>7.241984</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>0</v>
@@ -3781,7 +3781,7 @@
         <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>2.351222</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.188901</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.121301</v>
       </c>
     </row>
     <row r="111">
@@ -8477,7 +8477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U340"/>
+  <dimension ref="A1:U348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19186,7 +19186,11 @@
           <t>License and royalty liability accretion expense (note 9)</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -30988,10 +30992,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G232" s="5" t="n">
+        <v>2.979287</v>
       </c>
       <c r="H232" s="5" t="n">
         <v>1.578891</v>
@@ -31067,10 +31069,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G233" s="5" t="n">
+        <v>0.476575</v>
       </c>
       <c r="H233" s="5" t="n">
         <v>-0.134442</v>
@@ -31139,7 +31139,7 @@
         <v>0.324678</v>
       </c>
       <c r="G234" s="5" t="n">
-        <v>0.225821</v>
+        <v>0.224062</v>
       </c>
       <c r="H234" s="5" t="n">
         <v>0.040885</v>
@@ -31288,15 +31288,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G236" s="5" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="H236" s="5" t="n">
+        <v>2.205231</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
@@ -31587,12 +31583,10 @@
         <v>1.323416</v>
       </c>
       <c r="G240" s="5" t="n">
-        <v>1.799619</v>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.802323</v>
+      </c>
+      <c r="H240" s="5" t="n">
+        <v>7.761028</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
@@ -31663,10 +31657,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G241" s="5" t="n">
+        <v>0.001759</v>
       </c>
       <c r="H241" s="5" t="n">
         <v>0.004461</v>
@@ -38491,15 +38483,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G311" s="5" t="n">
+        <v>0.414705</v>
+      </c>
+      <c r="H311" s="5" t="n">
+        <v>0.017565</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
@@ -38691,15 +38679,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G313" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H313" s="5" t="n">
+        <v>-5e-08</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
@@ -39465,10 +39449,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G321" s="5" t="n">
+        <v>2.436577</v>
       </c>
       <c r="H321" s="5" t="n">
         <v>1.477411</v>
@@ -40532,10 +40514,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G332" s="5" t="n">
+        <v>-6.724221</v>
       </c>
       <c r="H332" s="5" t="n">
         <v>-6.724221</v>
@@ -40629,10 +40609,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G333" s="5" t="n">
+        <v>-5.08416</v>
       </c>
       <c r="H333" s="5" t="n">
         <v>-5.08416</v>
@@ -40709,32 +40687,34 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
+          <t>MayM  31             May 31</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
       <c r="D334" t="inlineStr">
         <is>
           <t>TotalRevenue</t>
         </is>
       </c>
-      <c r="E334" s="5" t="n">
-        <v>5.533685</v>
-      </c>
-      <c r="F334" s="5" t="n">
-        <v>4.13845</v>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G334" s="5" t="n">
         <v>3.455862</v>
       </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H334" s="5" t="n">
+        <v>14.444449</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -40810,28 +40790,34 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Cost of goods sold</t>
+          <t>Direct expenses</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Purchases and other direct costs</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
-      <c r="E335" s="5" t="n">
-        <v>4.62198</v>
-      </c>
-      <c r="F335" s="5" t="n">
-        <v>3.016449</v>
+          <t>Depreciation 1</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G335" s="5" t="n">
-        <v>2.436577</v>
-      </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.128005</v>
+      </c>
+      <c r="H335" s="5" t="n">
+        <v>0.00148</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -40907,32 +40893,30 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Cost of goods sold</t>
+          <t>Selling expenses</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
-      <c r="E336" s="5" t="n">
-        <v>0.911705</v>
-      </c>
-      <c r="F336" s="5" t="n">
-        <v>1.122001</v>
+          <t>Wages and benefits 1</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G336" s="5" t="n">
-        <v>1.019285</v>
-      </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.114423</v>
+      </c>
+      <c r="H336" s="5" t="n">
+        <v>0.064346</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -41013,7 +40997,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Interest (note 15)</t>
+          <t>Loss from operations before interest</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
@@ -41022,16 +41006,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F337" s="5" t="n">
-        <v>0.395302</v>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G337" s="5" t="n">
-        <v>0.454586</v>
-      </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.672367</v>
+      </c>
+      <c r="H337" s="5" t="n">
+        <v>-11.222727</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -41112,27 +41096,29 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Interest expense (note 15)</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E338" s="5" t="n">
-        <v>0.129617</v>
-      </c>
-      <c r="F338" s="5" t="n">
-        <v>0.130711</v>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G338" s="5" t="n">
-        <v>0.128005</v>
-      </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.454586</v>
+      </c>
+      <c r="H338" s="5" t="n">
+        <v>5.517334</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -41208,28 +41194,34 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Basic and fully diluted</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr"/>
-      <c r="E339" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="F339" s="5" t="n">
-        <v>-2e-08</v>
+          <t>Net loss and comprehensive loss for the yyear</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G339" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.126953</v>
+      </c>
+      <c r="H339" s="5" t="n">
+        <v>-16.440061</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -41305,92 +41297,890 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
+          <t>Capital          Surplus               Deficit          Deficiency</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Comprehensive loss for the period - -</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G340" s="5" t="n">
+        <v>-1.640061</v>
+      </c>
+      <c r="H340" s="5" t="n">
+        <v>-1.640061</v>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Capital          Surplus               Deficit          Deficiency</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Balance at June 1, 2010 12,921,322 182,400</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G341" s="5" t="n">
+        <v>-3.957207</v>
+      </c>
+      <c r="H341" s="5" t="n">
+        <v>-17.060929</v>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E342" s="5" t="n">
+        <v>5.533685</v>
+      </c>
+      <c r="F342" s="5" t="n">
+        <v>4.13845</v>
+      </c>
+      <c r="G342" s="5" t="n">
+        <v>3.455862</v>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Cost of goods sold</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Purchases and other direct costs</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" s="5" t="n">
+        <v>4.62198</v>
+      </c>
+      <c r="F343" s="5" t="n">
+        <v>3.016449</v>
+      </c>
+      <c r="G343" s="5" t="n">
+        <v>2.436577</v>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Cost of goods sold</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
+      <c r="E344" s="5" t="n">
+        <v>0.911705</v>
+      </c>
+      <c r="F344" s="5" t="n">
+        <v>1.122001</v>
+      </c>
+      <c r="G344" s="5" t="n">
+        <v>1.019285</v>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
           <t>General and administrative expenses</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr">
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Interest (note 15)</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F345" s="5" t="n">
+        <v>0.395302</v>
+      </c>
+      <c r="G345" s="5" t="n">
+        <v>0.454586</v>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E346" s="5" t="n">
+        <v>0.129617</v>
+      </c>
+      <c r="F346" s="5" t="n">
+        <v>0.130711</v>
+      </c>
+      <c r="G346" s="5" t="n">
+        <v>0.128005</v>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Loss per share</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Basic and fully diluted</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="F347" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="G347" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
         <is>
           <t>Interest (note 16)</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
-      <c r="E340" s="5" t="n">
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" s="5" t="n">
         <v>0.342524</v>
       </c>
-      <c r="F340" s="5" t="n">
+      <c r="F348" s="5" t="n">
         <v>0.395302</v>
       </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U340" t="inlineStr">
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
         <is>
           <t>-</t>
         </is>
